--- a/artfynd/A 28500-2025 artfynd.xlsx
+++ b/artfynd/A 28500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128036166</v>
       </c>
       <c r="B2" t="n">
-        <v>109286</v>
+        <v>109294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28500-2025 artfynd.xlsx
+++ b/artfynd/A 28500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128036166</v>
       </c>
       <c r="B2" t="n">
-        <v>109294</v>
+        <v>109295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28500-2025 artfynd.xlsx
+++ b/artfynd/A 28500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128036166</v>
       </c>
       <c r="B2" t="n">
-        <v>109295</v>
+        <v>109296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28500-2025 artfynd.xlsx
+++ b/artfynd/A 28500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128036166</v>
       </c>
       <c r="B2" t="n">
-        <v>109296</v>
+        <v>109297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28500-2025 artfynd.xlsx
+++ b/artfynd/A 28500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128036166</v>
       </c>
       <c r="B2" t="n">
-        <v>109297</v>
+        <v>109305</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28500-2025 artfynd.xlsx
+++ b/artfynd/A 28500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128036166</v>
       </c>
       <c r="B2" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28500-2025 artfynd.xlsx
+++ b/artfynd/A 28500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128036166</v>
       </c>
       <c r="B2" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28500-2025 artfynd.xlsx
+++ b/artfynd/A 28500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128036166</v>
       </c>
       <c r="B2" t="n">
-        <v>109422</v>
+        <v>109444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28500-2025 artfynd.xlsx
+++ b/artfynd/A 28500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128036166</v>
       </c>
       <c r="B2" t="n">
-        <v>109444</v>
+        <v>109589</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,7 +768,11 @@
           <t>Mikael Hagström</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28500-2025 artfynd.xlsx
+++ b/artfynd/A 28500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128036166</v>
       </c>
       <c r="B2" t="n">
-        <v>109589</v>
+        <v>109618</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28500-2025 artfynd.xlsx
+++ b/artfynd/A 28500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128036166</v>
       </c>
       <c r="B2" t="n">
-        <v>109618</v>
+        <v>109630</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28500-2025 artfynd.xlsx
+++ b/artfynd/A 28500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128036166</v>
       </c>
       <c r="B2" t="n">
-        <v>109630</v>
+        <v>109631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28500-2025 artfynd.xlsx
+++ b/artfynd/A 28500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128036166</v>
       </c>
       <c r="B2" t="n">
-        <v>109631</v>
+        <v>109636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28500-2025 artfynd.xlsx
+++ b/artfynd/A 28500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128036166</v>
       </c>
       <c r="B2" t="n">
-        <v>109636</v>
+        <v>109640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28500-2025 artfynd.xlsx
+++ b/artfynd/A 28500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128036166</v>
       </c>
       <c r="B2" t="n">
-        <v>109640</v>
+        <v>109642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28500-2025 artfynd.xlsx
+++ b/artfynd/A 28500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128036166</v>
       </c>
       <c r="B2" t="n">
-        <v>109642</v>
+        <v>109652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28500-2025 artfynd.xlsx
+++ b/artfynd/A 28500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128036166</v>
       </c>
       <c r="B2" t="n">
-        <v>109652</v>
+        <v>109656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28500-2025 artfynd.xlsx
+++ b/artfynd/A 28500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128036166</v>
       </c>
       <c r="B2" t="n">
-        <v>109656</v>
+        <v>109659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28500-2025 artfynd.xlsx
+++ b/artfynd/A 28500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128036166</v>
       </c>
       <c r="B2" t="n">
-        <v>109659</v>
+        <v>109660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28500-2025 artfynd.xlsx
+++ b/artfynd/A 28500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128036166</v>
       </c>
       <c r="B2" t="n">
-        <v>109660</v>
+        <v>110077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
